--- a/services/agent-orchestrator/mock_erp.xlsx
+++ b/services/agent-orchestrator/mock_erp.xlsx
@@ -4258,7 +4258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4485,6 +4485,186 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>2026-09-04T23:30:59.824655</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DEL0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SO0046</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DISPATCHED</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:29:34.000890</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DEL0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SO0047</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DISPATCHED</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:35:15.639428</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DEL0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SO0048</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DISPATCHED</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:49:09.914692</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DEL0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SO0049</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DISPATCHED</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:00:55.822696</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4802,6 +4982,242 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>2026-09-04T23:15:21.668344</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INV0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SO0046</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEL0005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>800</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Full delivery completed; invoice will be generated for the delivered items.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:29:34.968393</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INV0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SO0047</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEL0006</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>800</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Full delivery completed.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:35:16.472093</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INV0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SO0048</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEL0007</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>800</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Full delivery completed; invoice will be generated for the delivered quantity.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:49:12.649445</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INV0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SO0049</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEL0008</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>800</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Full delivery completed; invoice will be generated for the delivered items.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:00:56.643534</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5564,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5163,7 +5579,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>300</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24">
@@ -8201,7 +8617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10467,6 +10883,195 @@
       <c r="K45" t="inlineStr">
         <is>
           <t>2026-09-04T23:31:11.218371</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SO0046</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>800</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:29:33.027164</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SO0047</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" t="n">
+        <v>800</v>
+      </c>
+      <c r="H47" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:35:14.678550</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SO0048</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" t="n">
+        <v>800</v>
+      </c>
+      <c r="H48" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:49:08.907341</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SO0049</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Coastal Electronics Group</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>800</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:00:54.824741</t>
         </is>
       </c>
     </row>
@@ -11526,7 +12131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11916,6 +12521,181 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RSV0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SO0046</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PLANT01</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:29:33.958568</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RSV0011</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SO0046</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PLANT02</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:29:33.958568</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RSV0012</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SO0047</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PLANT02</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:35:15.596366</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RSV0013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SO0048</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PLANT02</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:49:09.842523</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RSV0014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SO0049</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wireless Mouse</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PLANT02</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:00:55.774199</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
